--- a/1_Data/Wang_2016_JEPHPP/Exp2/Codebook_Wang_2016_JEPHPP_Exp2_Clean.xlsx
+++ b/1_Data/Wang_2016_JEPHPP/Exp2/Codebook_Wang_2016_JEPHPP_Exp2_Clean.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,17 +551,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Matching</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Matching = shape-label pair conforms to the new (post-switch) assignment; Nonmatching = re-paired; NA in Association phase</t>
+          <t>Task type: the kind of shape-label matching task performed in the trial (default self-matching; other tasks e.g. facialExpression-matching, monetaryValue-matching, self-pseudoWords)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Matching; NA; Nonmatching</t>
+          <t>self-matching</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -573,17 +573,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Label_Origin_Identity</t>
+          <t>Matching</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Displayed label as in raw data (verbatim); NA in Association phase</t>
+          <t>Matching = shape-label pair conforms to the new (post-switch) assignment; Nonmatching = re-paired; NA in Association phase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NA; friend; self; stranger</t>
+          <t>Matching; NA; Nonmatching</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -595,17 +595,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Label_English_Identity</t>
+          <t>Label_Origin_Identity</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>English canonical form of label: Self/Friend/Stranger; NA in Association phase</t>
+          <t>Displayed label as in raw data (verbatim); NA in Association phase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>NA; friend; self; stranger</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -617,12 +617,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Label_Standardized_Identity</t>
+          <t>Label_English_Identity</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Standardized identity: Self; Close; Stranger; NA in Association phase</t>
+          <t>English canonical form of label: Self/Friend/Stranger; NA in Association phase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -639,17 +639,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shape_Origin_Identity</t>
+          <t>Label_Standardized_Identity</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shape identity as in raw data (Identity column = the person the shape was associated with in Part 1)</t>
+          <t>Standardized identity: Self; Close; Stranger; NA in Association phase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Friend; Self; Stranger</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shape_English_Identity</t>
+          <t>Shape_Origin_Identity</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>English canonical form: Self/Friend/Stranger</t>
+          <t>Shape identity as in raw data (Identity column = the person the shape was associated with in Part 1)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -683,17 +683,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shape_Standardized_Identity</t>
+          <t>Shape_English_Identity</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Standardized identity: Self; Close; Stranger</t>
+          <t>English canonical form: Self/Friend/Stranger</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Close; Self; Stranger</t>
+          <t>Friend; Self; Stranger</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -705,17 +705,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Shape_Standardized_Identity</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Response key: m = match, n = mismatch (keys counterbalanced across participants per paper); NA = no response</t>
+          <t>Standardized identity: Self; Close; Stranger</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NA; b; m; n</t>
+          <t>Close; Self; Stranger</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -727,39 +727,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RT_ms</t>
+          <t>Response</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Reaction time in milliseconds; NA = no response</t>
+          <t>Response key: m = match, n = mismatch (keys counterbalanced across participants per paper); NA = no response</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>NA; b; m; n</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Numerical</t>
+          <t>Categorical</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RT_sec</t>
+          <t>RT_ms</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Reaction time in seconds (RT_ms/1000); NA = no response</t>
+          <t>Reaction time in milliseconds; NA = no response</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -771,20 +771,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>RT_sec</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Reaction time in seconds (RT_ms/1000); NA = no response</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Numerical</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>ACC</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>1 = correct; 0 = incorrect; NA = no response</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>0; 1</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Categorical</t>
         </is>
